--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/NORTH_DAKOTA_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/NORTH_DAKOTA_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES</t>
+          <t>Aguascalientes</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C3">
@@ -410,12 +415,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C4">
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C5">
@@ -441,12 +451,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA SUR</t>
+          <t>Baja California Sur</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA PAZ</t>
+          <t>La Paz</t>
         </is>
       </c>
       <c r="C6">
@@ -457,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LOS CABOS</t>
+          <t>Los Cabos</t>
         </is>
       </c>
       <c r="C7">
@@ -470,9 +485,14 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C8">
@@ -485,12 +505,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHAMULA</t>
+          <t>Chamula</t>
         </is>
       </c>
       <c r="C9">
@@ -501,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHICOMUSELO</t>
+          <t>Chicomuselo</t>
         </is>
       </c>
       <c r="C10">
@@ -514,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COMITÁN DE DOMÍNGUEZ</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C11">
@@ -527,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COPAINALÁ</t>
+          <t>Copainalá</t>
         </is>
       </c>
       <c r="C12">
@@ -540,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FRONTERA COMALAPA</t>
+          <t>Frontera Comalapa</t>
         </is>
       </c>
       <c r="C13">
@@ -553,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HUIXTÁN</t>
+          <t>Huixtán</t>
         </is>
       </c>
       <c r="C14">
@@ -566,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA TRINITARIA</t>
+          <t>La Trinitaria</t>
         </is>
       </c>
       <c r="C15">
@@ -579,9 +629,14 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OCOTEPEC</t>
+          <t>Ocotepec</t>
         </is>
       </c>
       <c r="C16">
@@ -592,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SIMOJOVEL</t>
+          <t>Simojovel</t>
         </is>
       </c>
       <c r="C17">
@@ -605,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C18">
@@ -620,12 +685,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BUENAVENTURA</t>
+          <t>Buenaventura</t>
         </is>
       </c>
       <c r="C19">
@@ -636,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C20">
@@ -649,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C21">
@@ -662,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C22">
@@ -675,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JUÁREZ</t>
+          <t>Juárez</t>
         </is>
       </c>
       <c r="C23">
@@ -688,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NUEVO CASAS GRANDES</t>
+          <t>Nuevo Casas Grandes</t>
         </is>
       </c>
       <c r="C24">
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C25">
@@ -716,12 +811,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AZCAPOTZALCO</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C26">
@@ -732,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C27">
@@ -745,9 +845,14 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IZTACALCO</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="C28">
@@ -758,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C29">
@@ -771,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C30">
@@ -786,12 +901,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COAHUILA DE ZARAGOZA</t>
+          <t>Coahuila De Zaragoza</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MONCLOVA</t>
+          <t>Monclova</t>
         </is>
       </c>
       <c r="C31">
@@ -802,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SAN JUAN DE SABINAS</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C32">
@@ -815,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TORREÓN</t>
+          <t>Torreón</t>
         </is>
       </c>
       <c r="C33">
@@ -828,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Coahuila De Zaragoza</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C34">
@@ -843,12 +973,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="C35">
@@ -859,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GUADALUPE VICTORIA</t>
+          <t>Guadalupe Victoria</t>
         </is>
       </c>
       <c r="C36">
@@ -872,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MEZQUITAL</t>
+          <t>Mezquital</t>
         </is>
       </c>
       <c r="C37">
@@ -885,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TEPEHUANES</t>
+          <t>Tepehuanes</t>
         </is>
       </c>
       <c r="C38">
@@ -898,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C39">
@@ -913,12 +1063,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CUERÁMARO</t>
+          <t>Cuerámaro</t>
         </is>
       </c>
       <c r="C40">
@@ -929,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IRAPUATO</t>
+          <t>Irapuato</t>
         </is>
       </c>
       <c r="C41">
@@ -942,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JARAL DEL PROGRESO</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C42">
@@ -955,9 +1115,14 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PÉNJAMO</t>
+          <t>Pénjamo</t>
         </is>
       </c>
       <c r="C43">
@@ -968,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ROMITA</t>
+          <t>Romita</t>
         </is>
       </c>
       <c r="C44">
@@ -981,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SILAO DE LA VICTORIA</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C45">
@@ -994,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C46">
@@ -1009,12 +1189,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PETATLÁN</t>
+          <t>Petatlán</t>
         </is>
       </c>
       <c r="C47">
@@ -1025,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TÉCPAN DE GALEANA</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C48">
@@ -1038,9 +1223,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C49">
@@ -1053,12 +1243,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HUEJUTLA DE REYES</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C50">
@@ -1069,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>IXMIQUILPAN</t>
+          <t>Ixmiquilpan</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PACHUCA DE SOTO</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C53">
@@ -1110,12 +1315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ARANDAS</t>
+          <t>Arandas</t>
         </is>
       </c>
       <c r="C54">
@@ -1126,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AYUTLA</t>
+          <t>Ayutla</t>
         </is>
       </c>
       <c r="C55">
@@ -1139,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LAGOS DE MORENO</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C56">
@@ -1152,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PIHUAMO</t>
+          <t>Pihuamo</t>
         </is>
       </c>
       <c r="C57">
@@ -1165,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SAN DIEGO DE ALEJANDRÍA</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C58">
@@ -1178,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TLAJOMULCO DE ZÚÑIGA</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C59">
@@ -1191,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UNIÓN DE TULA</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C60">
@@ -1204,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VILLA HIDALGO</t>
+          <t>Villa Hidalgo</t>
         </is>
       </c>
       <c r="C61">
@@ -1217,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C62">
@@ -1232,12 +1477,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>APATZINGÁN</t>
+          <t>Apatzingán</t>
         </is>
       </c>
       <c r="C63">
@@ -1248,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BUENAVISTA</t>
+          <t>Buenavista</t>
         </is>
       </c>
       <c r="C64">
@@ -1261,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LOS REYES</t>
+          <t>Los Reyes</t>
         </is>
       </c>
       <c r="C65">
@@ -1274,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TURICATO</t>
+          <t>Turicato</t>
         </is>
       </c>
       <c r="C66">
@@ -1287,9 +1547,14 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C67">
@@ -1302,12 +1567,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MORELOS</t>
+          <t>Morelos</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CUERNAVACA</t>
+          <t>Cuernavaca</t>
         </is>
       </c>
       <c r="C68">
@@ -1318,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C69">
@@ -1333,12 +1603,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SANTIAGO IXCUINTLA</t>
+          <t>Santiago Ixcuintla</t>
         </is>
       </c>
       <c r="C70">
@@ -1349,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C71">
@@ -1364,12 +1639,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NUEVO LEÓN</t>
+          <t>Nuevo León</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CADEREYTA JIMÉNEZ</t>
+          <t>Cadereyta Jiménez</t>
         </is>
       </c>
       <c r="C72">
@@ -1380,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C73">
@@ -1395,12 +1675,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE HUAJUAPAN DE LEÓN</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C74">
@@ -1411,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HUAJUAPAN DE LEÓN</t>
+          <t>Huajuapan De León</t>
         </is>
       </c>
       <c r="C75">
@@ -1424,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>OAXACA DE JUÁREZ</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C76">
@@ -1437,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAN ANTONINO MONTE VERDE</t>
+          <t>San Antonino Monte Verde</t>
         </is>
       </c>
       <c r="C77">
@@ -1450,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SAN BALTAZAR LOXICHA</t>
+          <t>San Baltazar Loxicha</t>
         </is>
       </c>
       <c r="C78">
@@ -1463,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAN JUAN MIXTEPEC -DTO. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C79">
@@ -1476,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SANTIAGO JAMILTEPEC</t>
+          <t>Santiago Jamiltepec</t>
         </is>
       </c>
       <c r="C80">
@@ -1489,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SANTIAGO PINOTEPA NACIONAL</t>
+          <t>Santiago Pinotepa Nacional</t>
         </is>
       </c>
       <c r="C81">
@@ -1502,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SANTOS REYES NOPALA</t>
+          <t>Santos Reyes Nopala</t>
         </is>
       </c>
       <c r="C82">
@@ -1515,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C83">
@@ -1530,12 +1855,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AJALPAN</t>
+          <t>Ajalpan</t>
         </is>
       </c>
       <c r="C84">
@@ -1546,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CHALCHICOMULA DE SESMA</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C85">
@@ -1559,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CHIGNAHUAPAN</t>
+          <t>Chignahuapan</t>
         </is>
       </c>
       <c r="C86">
@@ -1572,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CUAUTLANCINGO</t>
+          <t>Cuautlancingo</t>
         </is>
       </c>
       <c r="C87">
@@ -1585,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HUAUCHINANGO</t>
+          <t>Huauchinango</t>
         </is>
       </c>
       <c r="C88">
@@ -1598,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C89">
@@ -1611,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ZACAPOAXTLA</t>
+          <t>Zacapoaxtla</t>
         </is>
       </c>
       <c r="C90">
@@ -1624,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ZACATLÁN</t>
+          <t>Zacatlán</t>
         </is>
       </c>
       <c r="C91">
@@ -1637,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C92">
@@ -1652,12 +2017,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AMEALCO DE BONFIL</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C93">
@@ -1668,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EL MARQUÉS</t>
+          <t>El Marqués</t>
         </is>
       </c>
       <c r="C94">
@@ -1681,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HUIMILPAN</t>
+          <t>Huimilpan</t>
         </is>
       </c>
       <c r="C95">
@@ -1694,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="C96">
@@ -1707,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAN JUAN DEL RÍO</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C97">
@@ -1720,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C98">
@@ -1735,12 +2125,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>AQUISMÓN</t>
+          <t>Aquismón</t>
         </is>
       </c>
       <c r="C99">
@@ -1751,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RAYÓN</t>
+          <t>Rayón</t>
         </is>
       </c>
       <c r="C100">
@@ -1764,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="C101">
@@ -1777,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SANTA MARÍA DEL RÍO</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C102">
@@ -1790,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>TAMUÍN</t>
+          <t>Tamuín</t>
         </is>
       </c>
       <c r="C103">
@@ -1803,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>XILITLA</t>
+          <t>Xilitla</t>
         </is>
       </c>
       <c r="C104">
@@ -1816,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ZARAGOZA</t>
+          <t>Zaragoza</t>
         </is>
       </c>
       <c r="C105">
@@ -1829,9 +2249,14 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C106">
@@ -1844,12 +2269,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>COSALÁ</t>
+          <t>Cosalá</t>
         </is>
       </c>
       <c r="C107">
@@ -1860,9 +2285,14 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>CULIACÁN</t>
+          <t>Culiacán</t>
         </is>
       </c>
       <c r="C108">
@@ -1873,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ESCUINAPA</t>
+          <t>Escuinapa</t>
         </is>
       </c>
       <c r="C109">
@@ -1886,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C110">
@@ -1901,12 +2341,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ALAMOS</t>
+          <t>Alamos</t>
         </is>
       </c>
       <c r="C111">
@@ -1917,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>CAJEME</t>
+          <t>Cajeme</t>
         </is>
       </c>
       <c r="C112">
@@ -1930,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NACOZARI DE GARCÍA</t>
+          <t>Nacozari De García</t>
         </is>
       </c>
       <c r="C113">
@@ -1943,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C114">
@@ -1958,12 +2413,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BALANCÁN</t>
+          <t>Balancán</t>
         </is>
       </c>
       <c r="C115">
@@ -1974,9 +2429,14 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TENOSIQUE</t>
+          <t>Tenosique</t>
         </is>
       </c>
       <c r="C116">
@@ -1987,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C117">
@@ -2002,12 +2467,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TAMAULIPAS</t>
+          <t>Tamaulipas</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NUEVO LAREDO</t>
+          <t>Nuevo Laredo</t>
         </is>
       </c>
       <c r="C118">
@@ -2018,9 +2483,14 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>REYNOSA</t>
+          <t>Reynosa</t>
         </is>
       </c>
       <c r="C119">
@@ -2031,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TAMPICO</t>
+          <t>Tampico</t>
         </is>
       </c>
       <c r="C120">
@@ -2044,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>XICOTÉNCATL</t>
+          <t>Xicoténcatl</t>
         </is>
       </c>
       <c r="C121">
@@ -2057,9 +2537,14 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C122">
@@ -2072,12 +2557,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="C123">
@@ -2088,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C124">
@@ -2103,12 +2593,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ATLAHUILCO</t>
+          <t>Atlahuilco</t>
         </is>
       </c>
       <c r="C125">
@@ -2119,9 +2609,14 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>COATEPEC</t>
+          <t>Coatepec</t>
         </is>
       </c>
       <c r="C126">
@@ -2132,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CÓRDOBA</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="C127">
@@ -2145,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>HUEYAPAN DE OCAMPO</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C128">
@@ -2158,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ILAMATLÁN</t>
+          <t>Ilamatlán</t>
         </is>
       </c>
       <c r="C129">
@@ -2171,9 +2681,14 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>LAS CHOAPAS</t>
+          <t>Las Choapas</t>
         </is>
       </c>
       <c r="C130">
@@ -2184,9 +2699,14 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PASO DEL MACHO</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C131">
@@ -2197,9 +2717,14 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PÁNUCO</t>
+          <t>Pánuco</t>
         </is>
       </c>
       <c r="C132">
@@ -2210,9 +2735,14 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TEQUILA</t>
+          <t>Tequila</t>
         </is>
       </c>
       <c r="C133">
@@ -2223,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TEZONAPA</t>
+          <t>Tezonapa</t>
         </is>
       </c>
       <c r="C134">
@@ -2236,9 +2771,14 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>XALAPA</t>
+          <t>Xalapa</t>
         </is>
       </c>
       <c r="C135">
@@ -2249,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZONGOLICA</t>
+          <t>Zongolica</t>
         </is>
       </c>
       <c r="C136">
@@ -2262,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C137">
@@ -2277,12 +2827,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RÍO GRANDE</t>
+          <t>Río Grande</t>
         </is>
       </c>
       <c r="C138">
@@ -2293,9 +2843,14 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C139">
@@ -2308,7 +2863,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C140">
@@ -2316,41 +2871,6 @@
       </c>
       <c r="D140">
         <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
